--- a/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 8,48</t>
+          <t>-3,46; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,6</t>
+          <t>-6,49; 5,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 6,45</t>
+          <t>-16,57; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 16,86</t>
+          <t>-12,48; 16,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 526,45</t>
+          <t>-61,25; 463,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-84,21; 225,33</t>
+          <t>-80,94; 255,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 42,8</t>
+          <t>-60,34; 33,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 92,04</t>
+          <t>-33,91; 79,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 6,22</t>
+          <t>-4,98; 6,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,01</t>
+          <t>-7,04; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 7,81</t>
+          <t>-8,83; 8,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 3,43</t>
+          <t>-17,79; 3,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 130,49</t>
+          <t>-48,27; 147,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 51,32</t>
+          <t>-81,6; 70,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 51,36</t>
+          <t>-36,63; 53,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 9,89</t>
+          <t>-37,14; 9,65</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,35</t>
+          <t>-7,15; 5,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,93</t>
+          <t>-1,58; 8,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 5,76</t>
+          <t>-15,18; 5,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 10,95</t>
+          <t>-13,18; 10,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,93; 147,46</t>
+          <t>-71,41; 152,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,67; —</t>
+          <t>-59,06; 1127,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 38,56</t>
+          <t>-55,17; 38,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 70,47</t>
+          <t>-48,01; 77,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 6,98</t>
+          <t>-5,67; 7,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 5,72</t>
+          <t>-9,72; 4,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 13,06</t>
+          <t>-4,99; 13,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 15,66</t>
+          <t>-6,95; 15,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 184,42</t>
+          <t>-58,84; 209,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 86,02</t>
+          <t>-69,06; 81,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 109,33</t>
+          <t>-23,71; 113,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 68,15</t>
+          <t>-21,35; 62,14</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,07</t>
+          <t>-2,55; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,05</t>
+          <t>-3,59; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,28</t>
+          <t>-5,43; 4,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,65</t>
+          <t>-7,81; 3,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 77,58</t>
+          <t>-30,53; 69,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 44,06</t>
+          <t>-46,43; 50,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 24,11</t>
+          <t>-25,77; 23,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 13,52</t>
+          <t>-22,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 8,34</t>
+          <t>-3,42; 8,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 5,77</t>
+          <t>-5,64; 5,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 5,37</t>
+          <t>-16,96; 4,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 16,36</t>
+          <t>-13,08; 16,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,25; 463,97</t>
+          <t>-59,52; 482,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 255,53</t>
+          <t>-75,63; 203,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 33,47</t>
+          <t>-60,55; 32,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 79,4</t>
+          <t>-33,59; 80,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,32</t>
+          <t>-5,03; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,18</t>
+          <t>-7,08; 1,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 8,43</t>
+          <t>-8,48; 8,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 3,56</t>
+          <t>-16,35; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 147,72</t>
+          <t>-49,11; 126,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,6; 70,85</t>
+          <t>-76,16; 48,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 53,68</t>
+          <t>-35,3; 58,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 9,65</t>
+          <t>-35,49; 12,06</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,46</t>
+          <t>-6,63; 5,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,54</t>
+          <t>-1,91; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 5,63</t>
+          <t>-14,7; 5,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 10,59</t>
+          <t>-13,46; 10,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 152,47</t>
+          <t>-68,48; 169,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 1127,04</t>
+          <t>-71,47; 1034,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 38,74</t>
+          <t>-53,42; 39,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 77,45</t>
+          <t>-49,77; 74,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 7,32</t>
+          <t>-5,81; 7,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 4,69</t>
+          <t>-9,35; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 13,46</t>
+          <t>-4,47; 13,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 15,08</t>
+          <t>-7,42; 15,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 209,58</t>
+          <t>-58,12; 209,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,06; 81,04</t>
+          <t>-67,67; 87,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 113,2</t>
+          <t>-22,65; 114,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 62,14</t>
+          <t>-20,71; 66,06</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,63</t>
+          <t>-2,48; 3,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,42</t>
+          <t>-3,58; 2,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,1</t>
+          <t>-5,4; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,82</t>
+          <t>-7,65; 4,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 69,16</t>
+          <t>-31,15; 75,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 50,32</t>
+          <t>-45,53; 46,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 23,68</t>
+          <t>-24,55; 26,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 13,13</t>
+          <t>-22,3; 15,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 8,23</t>
+          <t>-3,17; 8,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,61</t>
+          <t>-6,47; 5,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 4,56</t>
+          <t>-16,86; 6,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 16,36</t>
+          <t>-13,37; 15,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,52; 482,79</t>
+          <t>-52,05; 526,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,63; 203,0</t>
+          <t>-84,21; 225,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,55; 32,06</t>
+          <t>-59,72; 42,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 80,88</t>
+          <t>-34,65; 76,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-6,67</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,34%</t>
+          <t>-14,97%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,29</t>
+          <t>-5,21; 6,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 1,49</t>
+          <t>-7,3; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 8,8</t>
+          <t>-9,34; 7,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 4,57</t>
+          <t>-17,2; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 126,35</t>
+          <t>-51,7; 130,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 48,96</t>
+          <t>-80,75; 51,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,3; 58,62</t>
+          <t>-38,67; 51,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 12,06</t>
+          <t>-34,7; 11,15</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,85%</t>
+          <t>-9,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 5,98</t>
+          <t>-7,28; 5,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 9,39</t>
+          <t>-2,06; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 5,84</t>
+          <t>-14,93; 5,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 10,53</t>
+          <t>-15,29; 9,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 169,95</t>
+          <t>-68,93; 147,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 1034,73</t>
+          <t>-59,67; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 39,42</t>
+          <t>-55,08; 38,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 74,59</t>
+          <t>-51,86; 56,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,67</t>
+          <t>-5,4; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 5,53</t>
+          <t>-9,35; 5,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 13,58</t>
+          <t>-4,76; 13,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 15,14</t>
+          <t>-8,57; 15,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 209,5</t>
+          <t>-57,8; 184,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 87,11</t>
+          <t>-69,25; 86,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 114,43</t>
+          <t>-23,44; 109,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 66,06</t>
+          <t>-22,25; 62,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,64%</t>
+          <t>-6,99%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,83</t>
+          <t>-2,18; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,19</t>
+          <t>-3,45; 2,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,63</t>
+          <t>-5,33; 4,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,39</t>
+          <t>-8,31; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,54</t>
+          <t>-28,06; 77,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 46,43</t>
+          <t>-43,59; 44,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 26,7</t>
+          <t>-24,63; 24,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 15,02</t>
+          <t>-22,64; 10,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-24,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.122235807423612</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.1972916148687026</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-5.422209314921078</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.2428642894871824</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4911602071832771</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.03749061567546598</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.246761244327801</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.007686973945225462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; 8,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 5,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-16,86; 6,45</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-13,37; 15,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-52,05; 526,45</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-84,21; 225,33</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-59,72; 42,8</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-34,65; 76,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.16647264966882</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.473909024996055</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-16.86187317057476</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-13.3668137007817</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5204936719302238</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8420556903311732</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5971757459890751</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3464522978497527</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.47533753604851</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.598338502953289</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.448926692368735</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.59596446520661</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>5.264453294103515</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.253344837938039</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.4280377826713361</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.7648073104094308</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,67</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-36,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-14,97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 6,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,3; 2,01</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,34; 7,81</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,2; 4,39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-51,7; 130,49</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-80,75; 51,32</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-38,67; 51,36</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-34,7; 11,15</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3517177900774826</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.279651833754972</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3308401107459169</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.67174851824136</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.04488810838188146</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3611329569310735</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.01687093083052959</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1496577431168391</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>117,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-18,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,91%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.214708092615976</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.302851385177646</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.339629985886148</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.20364331275798</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5170359962683398</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8074896951451599</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3867253130665229</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.34702159336021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; 5,35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,06; 8,93</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,93; 5,76</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-15,29; 9,1</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-68,93; 147,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-59,67; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-55,08; 38,56</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-51,86; 56,56</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.216389043456982</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.013513136406424</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.812223118171937</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.394154458988564</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.304890972704168</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5131681081449883</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.513579828070963</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1114681114138316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,295 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-19,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.8410580256129396</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.226358105393966</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.843562191420727</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.219156046805118</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.116403700365379</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.178341494588661</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1823662244859157</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.0990723587048576</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,4; 6,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,35; 5,72</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 13,06</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,57; 15,21</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-57,8; 184,42</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-69,25; 86,02</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-23,44; 109,33</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-22,25; 62,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.278110238447953</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.061022948105733</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-14.93030959345335</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-15.28865158768276</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6893263838216837</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5966707309756951</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5508006655054981</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5185611880167774</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.352653009324657</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.933025920595362</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.755502646628009</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.104164000878399</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.474556319386119</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>0.3856107395134102</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.5655894475867451</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8421056175469871</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.962802706559994</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.119506762268591</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.057755046422007</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1219642486127118</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1923435465136383</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2472277726886104</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1324391245728319</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.403387807222391</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.352216567446023</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.758382323124871</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.57052540491156</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5780401692881819</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6925326436805778</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2344250293352083</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.222543976811389</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.982758902855567</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.71679228206817</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.05689015692025</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.21014772245411</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.844208816452557</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8601508688406666</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.093328000994651</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6207579672553186</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 4,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,45; 2,05</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 4,28</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-8,31; 2,95</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-28,06; 77,58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-43,59; 44,06</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-24,63; 24,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-22,64; 10,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.6611939300429026</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5777745524376786</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5809774516852995</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.356307878525499</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.09907249671699263</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.09110525685313917</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02972046326396993</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06989419700704971</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.17772021726706</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.453172613381513</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.331072946638328</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.306906683862545</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2805663234190969</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.435860963293157</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2462828515585462</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.226380468656766</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.068503744071744</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.051364992515159</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.276837228951448</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.94573267037387</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7757620599852281</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.44057784555687</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2410626470452018</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1019280319824159</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1115,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
